--- a/artfynd/A 25923-2026 artfynd.xlsx
+++ b/artfynd/A 25923-2026 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>134359351</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25923-2026 artfynd.xlsx
+++ b/artfynd/A 25923-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102612255</v>
+        <v>123762876</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stigsbo Jan-Olofs, Hedemora, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571162.0491961198</v>
+        <v>571241</v>
       </c>
       <c r="R2" t="n">
-        <v>6702738.897978535</v>
+        <v>6702719</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123762876</v>
+        <v>110142662</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,37 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Stigsbo, Dlr</t>
+          <t>Vreten, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571241</v>
+        <v>571185</v>
       </c>
       <c r="R3" t="n">
-        <v>6702719</v>
+        <v>6702765</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +838,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134359349</v>
+        <v>102612032</v>
       </c>
       <c r="B4" t="n">
-        <v>8449</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,42 +891,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Stigsbo, Dlr</t>
+          <t>Stigsbo Jan-Olofs, Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571225</v>
+        <v>571184</v>
       </c>
       <c r="R4" t="n">
-        <v>6702702</v>
+        <v>6702764</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,22 +947,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,64 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134359351</v>
+        <v>110629314</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Stigsbo, Dlr</t>
+          <t>Vreten, Vreten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571202</v>
+        <v>571156</v>
       </c>
       <c r="R5" t="n">
-        <v>6702661</v>
+        <v>6702775</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,22 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1079,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,6 +1094,2211 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112419347</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vreten, Vreten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571160</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6702772</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128473408</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övre Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571020</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702735</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104354141</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702733</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110142661</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vreten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571185</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702765</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111202708</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571186</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6702757</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120636765</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ballsberget östra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571186</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6702751</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134359349</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Övre Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571225</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6702702</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96619820</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571247</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6702744</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96620397</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stigsbo Jan-Olofs 175, Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571183</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6702768</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>102612048</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stigsbo Jan-Olofs, Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571184</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6702764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>102612255</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stigsbo Jan-Olofs, Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571162</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6702739</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110142646</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vreten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571170</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6702768</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110142675</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vreten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571184</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6702761</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>110142706</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vreten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571186</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6702758</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111202722</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sandänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571187</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6702754</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter, blomning</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118311686</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dammänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571186</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6702748</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118311687</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dammänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>571186</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6702750</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118311688</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dammänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>571165</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6702756</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120636761</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dammänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>571183</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6702753</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134359351</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Övre Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>571202</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6702661</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25923-2026 artfynd.xlsx
+++ b/artfynd/A 25923-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123762876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110142662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102612032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110629314</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419347</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473408</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104354141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110142661</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111202708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120636765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134359349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96619820</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96620397</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102612048</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102612255</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2400,6 +2480,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110142646</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2512,6 +2597,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110142675</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110142706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111202722</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2841,6 +2941,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311686</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2955,6 +3060,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311687</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3069,6 +3179,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311688</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3175,6 +3290,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120636761</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3299,8 +3419,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134359351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>